--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260805.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>151,535</t>
+          <t>149,535</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>29.35%</t>
+          <t>29.61%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,215</t>
+          <t>16,985</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.12%</t>
+          <t>8.19%</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>109,950</t>
+          <t>108,470</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>55,925</t>
+          <t>55,275</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.53%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>133,645</t>
+          <t>131,645</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.36%</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>65,620</t>
+          <t>64,730</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>72,205</t>
+          <t>71,235</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,225</t>
+          <t>6,125</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>49,885</t>
+          <t>49,215</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>20,133</t>
+          <t>19,883</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,725</t>
+          <t>21,425</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,44 +843,44 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>34,760</t>
+          <t>83,605</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>84,705</t>
+          <t>34,260</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,345</t>
+          <t>21,995</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>56,295</t>
+          <t>55,395</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -941,122 +941,122 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>29,248</t>
+          <t>28,848</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>39,320</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>39,920</t>
+          <t>21,180</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>21,470</t>
+          <t>64,548</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>65,498</t>
+          <t>12,691</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>12,851</t>
+          <t>8,660</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1073,34 +1073,34 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>23,468</t>
+          <t>23,118</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>10,566</t>
+          <t>79,815,301</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1117,56 +1117,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>139,845</t>
+          <t>137,945</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,305</t>
+          <t>10,436</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,052,927</t>
+          <t>20,005</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>21,567</t>
+          <t>21,277</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>17,471</t>
+          <t>17,221</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,39 +1217,39 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,500</t>
+          <t>46,940</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>54,827,557</t>
+          <t>40,750</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>47,690</t>
+          <t>12,655</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,005</t>
+          <t>1,238,909</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>64,940,500</t>
+          <t>100,228,500</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>685,982</t>
+          <t>2,923,980</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
